--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2761,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2769,12 +2809,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2788,7 +2828,7 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2824,7 +2864,1014 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1338,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1482,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1593,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1743,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1815,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1893,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,10 +1966,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2037,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2226,12 +2274,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2259,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,10 +2315,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2370,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3433,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3544,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3655,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3751,12 +3815,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3881,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3875,6 +3939,914 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1475,24 +1475,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1764,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1780,13 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1847,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq59，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2163,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2196,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2303,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq48，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2307,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,32 +2425,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2434,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,33 +2486,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2512,32 +2544,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2545,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,33 +2605,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2663,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2656,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,33 +2724,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2878,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2989,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3067,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3100,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3124,33 +3176,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3820,7 +3876,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4165,7 +4221,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4337,7 +4393,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4448,7 +4504,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4502,7 +4558,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4619,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4612,12 +4668,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4734,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4732,7 +4788,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4849,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4837,11 +4893,1038 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
         </is>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2893,32 +2893,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2954,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2970,13 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -3004,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3037,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3061,17 +3073,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3081,13 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3125,24 +3141,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3152,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3201,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3234,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3267,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,33 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3345,32 +3369,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3378,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,17 +3430,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3422,13 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3456,32 +3488,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3489,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,17 +3549,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3533,13 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3567,32 +3607,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3600,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3624,33 +3668,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3678,32 +3726,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3711,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3735,33 +3787,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3789,32 +3845,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3822,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3846,17 +3906,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3866,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3904,32 +3964,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3937,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3961,17 +4025,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3981,7 +4045,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -3991,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4019,32 +4083,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4052,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4076,32 +4144,32 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4134,32 +4202,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4167,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4191,37 +4263,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4321,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4282,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4290,10 +4362,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4393,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4471,32 +4559,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4504,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4528,17 +4620,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4548,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4658,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4673,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4773,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4788,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4903,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4964,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5244,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5359,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5474,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5589,7 +5681,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5810,12 +5902,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5920,13 +6012,822 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>21/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>19/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,13 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1788,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2033,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2040,7 +2044,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,13 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2397,7 +2405,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2514,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2628,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2635,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2873,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4063,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4247,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4301,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4354,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4420,7 +4428,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4448,32 +4456,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4481,7 +4493,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4517,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4525,13 +4537,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4569,12 +4585,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4596,7 +4612,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4661,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4678,32 +4694,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4711,7 +4731,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4755,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4755,17 +4775,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4793,32 +4813,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4826,7 +4850,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4874,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,17 +4894,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4908,32 +4932,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4941,7 +4969,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4993,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4985,17 +5013,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5051,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5056,7 +5088,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5112,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5132,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5170,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5171,7 +5207,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5231,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,13 +5251,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5249,32 +5289,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5282,7 +5326,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,37 +5350,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5364,32 +5408,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5397,7 +5445,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,17 +5469,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5441,17 +5489,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,7 +5599,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5566,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5681,7 +5729,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5792,7 +5840,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6022,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6137,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6252,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6367,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6482,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6597,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6702,17 +6750,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6817,17 +6865,580 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>19/27</t>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,13 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,22 +2981,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,14 +3457,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,22 +3695,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3819,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4132,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4186,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4251,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4286,7 +4290,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4301,7 +4305,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4670,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4735,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4785,7 +4789,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4854,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5146,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5330,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5380,7 +5384,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5449,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,7 +5488,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5499,7 +5503,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5527,32 +5531,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5560,7 +5568,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5592,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5604,17 +5612,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5642,32 +5650,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5675,7 +5687,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5711,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5719,17 +5731,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5757,32 +5769,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5790,7 +5806,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5830,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5834,13 +5850,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5868,32 +5888,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5901,7 +5925,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,37 +5949,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5983,32 +6007,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6016,7 +6044,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,37 +6068,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6098,32 +6126,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6131,7 +6163,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6187,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6175,17 +6207,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6213,32 +6245,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6246,7 +6282,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,37 +6306,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6328,32 +6364,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6361,7 +6401,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6425,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6405,17 +6445,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6516,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6555,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,7 +6570,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6685,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6800,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6875,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7047,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7158,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7212,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7428,15 +7468,705 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>147.0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
         </is>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,14 +1426,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>142.5</t>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,18 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3476,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3660,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,12 +3709,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3779,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3824,12 +3828,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,14 +3937,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -3948,7 +3952,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4071,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4136,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4176,12 +4180,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4251,7 +4255,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4295,17 +4299,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4620,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4655,14 +4659,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4739,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4774,22 +4778,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4858,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4898,17 +4902,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5031,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5096,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5131,14 +5135,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>142.5</t>
@@ -5146,7 +5150,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5388,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5453,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5503,7 +5507,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5572,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5622,7 +5626,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5864,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5929,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5979,7 +5983,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6048,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6098,7 +6102,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6221,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6255,24 +6259,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6282,7 +6286,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6331,12 +6335,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6378,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6401,7 +6405,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6450,12 +6454,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6483,32 +6487,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6516,7 +6524,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6548,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6560,17 +6568,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6598,32 +6606,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6631,7 +6643,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,17 +6667,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6675,12 +6687,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6713,32 +6725,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6746,7 +6762,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,37 +6786,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6828,32 +6844,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6861,7 +6881,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6905,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6905,17 +6925,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6943,12 +6963,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq55，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6976,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6984,10 +7004,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7054,32 +7086,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7087,7 +7123,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,33 +7147,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7292,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7424,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7593,7 +7633,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7933,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,15 +8198,590 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="AC65" s="2" t="inlineStr">
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
         </is>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2403,13 +2403,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,17 +2522,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2637,17 +2641,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2990,17 +2994,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,14 +3108,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3119,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,17 +3232,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3476,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3580,14 +3584,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -3595,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3952,7 +3956,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4075,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4259,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4309,7 +4313,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4374,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4425,7 +4429,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4436,7 +4440,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4674,7 +4678,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4793,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4862,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4907,12 +4911,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5150,7 +5154,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5254,7 +5258,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5269,7 +5273,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5497,17 +5501,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5576,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5616,17 +5620,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5749,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5868,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5973,17 +5977,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6092,17 +6096,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6290,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6340,7 +6344,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6528,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6578,7 +6582,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6766,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6816,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6854,24 +6858,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>118分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6881,7 +6885,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6930,12 +6934,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq55，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq60，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6996,7 +7000,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7058,7 +7062,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7127,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7177,7 +7181,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7320,32 +7324,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7353,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7377,17 +7385,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7397,13 +7405,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7431,32 +7443,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7464,7 +7480,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7488,17 +7504,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7508,17 +7524,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7546,32 +7562,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7579,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7623,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7623,17 +7643,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7661,32 +7681,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7694,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7742,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7738,17 +7762,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7776,32 +7800,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7809,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,17 +7861,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7853,17 +7881,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7952,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +8006,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8067,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8093,7 +8121,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8182,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8208,7 +8236,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8297,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8351,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8438,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8581,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8668,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8811,574 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6334,17 +6334,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7572,24 +7572,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7810,24 +7810,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7919,32 +7919,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7952,7 +7956,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7976,17 +7980,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7996,17 +8000,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8071,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8182,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8297,7 +8301,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8412,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8527,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8581,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8646,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8696,7 +8700,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9098,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9209,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9324,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9382,6 +9386,121 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3346,14 +3346,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>135.5</t>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4303,17 +4303,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6210,14 +6210,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>135.5</t>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,14 +6448,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6572,17 +6572,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7703,12 +7703,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8038,32 +8038,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8071,7 +8075,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8095,17 +8099,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8115,17 +8119,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8153,32 +8157,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8186,7 +8194,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8210,17 +8218,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8230,17 +8238,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8268,32 +8276,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8301,7 +8313,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,17 +8337,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8345,17 +8357,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8428,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8470,7 +8482,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8543,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8646,7 +8658,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8761,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8815,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8987,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9213,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9382,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9390,22 +9402,22 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9443,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,17 +9499,822 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
+      <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>137.3</t>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,22 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,14 +3465,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3941,22 +3941,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4787,17 +4787,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>137.3</t>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6810,17 +6810,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,14 +6924,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>137.3</t>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8114,14 +8114,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8167,24 +8167,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8286,12 +8286,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8352,22 +8352,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8395,32 +8395,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8428,7 +8432,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8452,17 +8456,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8472,17 +8476,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8547,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8582,7 +8586,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8597,7 +8601,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8625,32 +8629,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8658,7 +8666,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8682,37 +8690,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8740,32 +8748,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8773,7 +8785,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8797,17 +8809,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8817,17 +8829,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8855,12 +8867,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8888,7 +8900,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,10 +8908,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8938,7 +8966,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8966,32 +8994,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8999,7 +9031,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9023,17 +9055,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9043,17 +9075,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9196,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9372,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9426,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9509,7 +9541,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9602,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9624,7 +9656,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9739,7 +9771,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9854,7 +9886,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9969,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10084,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,7 +10231,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10314,7 +10346,808 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3108,22 +3108,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4668,17 +4668,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5139,22 +5139,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5263,17 +5263,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5496,14 +5496,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5972,14 +5972,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>140.7</t>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7757,14 +7757,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8514,32 +8514,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8547,7 +8551,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8571,17 +8575,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8591,17 +8595,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8670,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8720,7 +8724,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8758,24 +8762,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8785,7 +8789,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,22 +8828,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8876,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8900,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9004,24 +9008,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9031,7 +9035,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,22 +9074,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9224,32 +9228,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9257,7 +9265,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9281,17 +9289,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9301,17 +9309,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9339,32 +9347,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9372,7 +9384,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9408,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9416,17 +9428,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9454,32 +9466,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9487,7 +9503,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9511,17 +9527,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9531,17 +9547,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9569,32 +9585,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9602,7 +9622,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,17 +9646,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9646,17 +9666,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>154.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9737,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9756,7 +9776,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9771,7 +9791,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9886,7 +9906,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9967,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10001,7 +10021,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10116,7 +10136,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10231,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10346,7 +10366,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10461,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10576,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10748,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10802,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10917,7 +10937,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11147,7 +11167,697 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,17 +2755,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3822,22 +3822,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4184,17 +4184,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4544,22 +4544,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5025,17 +5025,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6215,17 +6215,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8119,17 +8119,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9476,24 +9476,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9595,12 +9595,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9661,17 +9661,17 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9704,32 +9704,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9737,7 +9741,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9761,17 +9765,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9781,17 +9785,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9819,32 +9823,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9852,7 +9860,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9876,32 +9884,32 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9934,32 +9942,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9967,7 +9979,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9991,37 +10003,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10049,32 +10061,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10082,7 +10098,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10106,37 +10122,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10164,32 +10180,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10197,7 +10217,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10221,17 +10241,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10241,17 +10261,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10279,32 +10299,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10312,7 +10336,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10336,17 +10360,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10356,17 +10380,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10451,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10481,7 +10505,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10533,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10542,7 +10570,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10566,17 +10594,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10586,17 +10614,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10685,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10768,7 +10796,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10822,7 +10850,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10911,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10937,7 +10965,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11026,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11052,7 +11080,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11195,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11282,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11397,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11512,7 +11540,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11627,7 +11655,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11742,7 +11770,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,17 +11875,937 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB96" s="2" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
-      <c r="AC96" s="2" t="inlineStr">
-        <is>
-          <t>9/30</t>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,17 +2641,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2870,22 +2870,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4668,17 +4668,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5620,17 +5620,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,22 +5853,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6929,17 +6929,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7762,17 +7762,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8357,17 +8357,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8595,17 +8595,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10256,14 +10256,14 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10418,32 +10418,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10451,7 +10455,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10475,17 +10479,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10495,17 +10499,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10543,12 +10547,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10570,7 +10574,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10619,12 +10623,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10652,32 +10656,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>16:51</t>
@@ -10685,7 +10693,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10709,17 +10717,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10729,13 +10737,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB86" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10763,32 +10775,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10796,7 +10812,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10820,17 +10836,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10840,17 +10856,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10878,32 +10894,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10911,7 +10931,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10935,17 +10955,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10955,17 +10975,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10993,32 +11013,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11026,7 +11050,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11050,17 +11074,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11070,17 +11094,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11219,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11223,32 +11247,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11256,7 +11284,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11280,37 +11308,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11338,32 +11366,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11371,7 +11403,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11395,17 +11427,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11415,17 +11447,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11486,7 +11518,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11540,7 +11572,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11633,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11716,7 +11748,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11770,7 +11802,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11798,12 +11830,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11831,7 +11863,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11839,10 +11871,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11885,7 +11933,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11994,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12000,7 +12048,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12109,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12176,7 +12224,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12230,7 +12278,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12339,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12345,7 +12393,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12454,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12460,7 +12508,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12569,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12636,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12751,7 +12799,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12805,7 +12853,237 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5263,17 +5263,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8833,17 +8833,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9079,17 +9079,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9309,17 +9309,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9428,17 +9428,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11257,24 +11257,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11600,32 +11600,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11633,7 +11637,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11657,17 +11661,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11677,17 +11681,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11715,32 +11719,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11748,7 +11756,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11772,17 +11780,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11792,17 +11800,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11843,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11863,7 +11871,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11933,7 +11941,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11961,32 +11969,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11994,7 +12006,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12018,17 +12030,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12038,17 +12050,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12076,32 +12088,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12109,7 +12125,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12133,17 +12149,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12153,17 +12169,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12240,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12278,7 +12294,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12322,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq46，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12339,7 +12355,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12347,10 +12363,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12393,7 +12425,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12486,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12569,7 +12601,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12623,7 +12655,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12716,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12738,7 +12770,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12831,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12853,7 +12885,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12946,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12968,7 +13000,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13061,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13078,12 +13110,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-浦东35路.xlsx
+++ b/data/export/2026-10-27-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6096,17 +6096,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7881,17 +7881,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq46，推进18站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12453,32 +12453,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12486,7 +12490,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12510,17 +12514,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12530,12 +12534,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12568,32 +12572,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12601,7 +12609,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12625,17 +12633,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12645,12 +12653,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12683,32 +12691,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12716,7 +12728,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12740,17 +12752,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12760,17 +12772,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12843,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12885,7 +12897,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12958,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13061,7 +13073,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13115,7 +13127,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
